--- a/Daily_Report/Top 7 broker List with its Turnover 2024-02-18.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-02-18.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="279">
   <si>
     <t>Date: 2024-02-18</t>
   </si>
@@ -62,106 +62,103 @@
     <t>Naasa Securities Co. Ltd.</t>
   </si>
   <si>
+    <t>Imperial Securities Co .Pvt.Limited</t>
+  </si>
+  <si>
+    <t>Agrawal Securities Pvt. Limited</t>
+  </si>
+  <si>
+    <t>Vision Securities Pvt.Limited</t>
+  </si>
+  <si>
+    <t>Dipshika Dhitopatra Karobar Co. Pvt.Limited</t>
+  </si>
+  <si>
+    <t>Nepal Stock House Pvt. Limited</t>
+  </si>
+  <si>
     <t>Sani Securities Company Limited</t>
   </si>
   <si>
-    <t>Dipshika Dhitopatra Karobar Co. Pvt.Limited</t>
-  </si>
-  <si>
-    <t>Vision Securities Pvt.Limited</t>
-  </si>
-  <si>
-    <t>Bhrikuti Stock Broking Co. Pvt. Ltd.</t>
-  </si>
-  <si>
-    <t>Premier Securites Company Limited</t>
-  </si>
-  <si>
-    <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
-  </si>
-  <si>
     <t>58</t>
   </si>
   <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
     <t>42</t>
   </si>
   <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>481,568,154.9</t>
-  </si>
-  <si>
-    <t>412,924,297.55</t>
-  </si>
-  <si>
-    <t>286,130,714.8</t>
-  </si>
-  <si>
-    <t>261,041,772.14</t>
-  </si>
-  <si>
-    <t>257,433,660.6</t>
-  </si>
-  <si>
-    <t>254,039,377.2</t>
-  </si>
-  <si>
-    <t>224,726,098.2</t>
-  </si>
-  <si>
-    <t>187,945,017.2</t>
-  </si>
-  <si>
-    <t>312,398,883.6</t>
-  </si>
-  <si>
-    <t>124,895,404.8</t>
-  </si>
-  <si>
-    <t>138,035,041.1</t>
-  </si>
-  <si>
-    <t>158,890,518.3</t>
-  </si>
-  <si>
-    <t>73,033,570.7</t>
-  </si>
-  <si>
-    <t>111,516,991.4</t>
-  </si>
-  <si>
-    <t>293,623,137.7</t>
-  </si>
-  <si>
-    <t>100,525,413.95</t>
-  </si>
-  <si>
-    <t>161,235,310.0</t>
-  </si>
-  <si>
-    <t>123,006,731.05</t>
-  </si>
-  <si>
-    <t>98,543,142.3</t>
-  </si>
-  <si>
-    <t>181,005,806.5</t>
-  </si>
-  <si>
-    <t>113,209,106.8</t>
+    <t>558,705,568.0</t>
+  </si>
+  <si>
+    <t>434,196,789.7</t>
+  </si>
+  <si>
+    <t>335,268,014.74</t>
+  </si>
+  <si>
+    <t>303,201,341.35</t>
+  </si>
+  <si>
+    <t>257,178,112.5</t>
+  </si>
+  <si>
+    <t>250,245,140.7</t>
+  </si>
+  <si>
+    <t>246,604,635.25</t>
+  </si>
+  <si>
+    <t>184,585,964.0</t>
+  </si>
+  <si>
+    <t>211,954,547.8</t>
+  </si>
+  <si>
+    <t>291,991,885.62</t>
+  </si>
+  <si>
+    <t>122,286,962.3</t>
+  </si>
+  <si>
+    <t>127,357,556.1</t>
+  </si>
+  <si>
+    <t>47,714,934.4</t>
+  </si>
+  <si>
+    <t>158,285,542.6</t>
+  </si>
+  <si>
+    <t>374,119,604.0</t>
+  </si>
+  <si>
+    <t>222,242,241.9</t>
+  </si>
+  <si>
+    <t>43,276,129.12</t>
+  </si>
+  <si>
+    <t>180,914,379.05</t>
+  </si>
+  <si>
+    <t>129,820,556.4</t>
+  </si>
+  <si>
+    <t>202,530,206.3</t>
+  </si>
+  <si>
+    <t>88,319,092.65</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -179,331 +176,343 @@
     <t>% of turnover</t>
   </si>
   <si>
-    <t>RFPL</t>
-  </si>
-  <si>
-    <t>33,855,957.5</t>
-  </si>
-  <si>
     <t>UNHPL</t>
   </si>
   <si>
-    <t>29,026,655.8</t>
+    <t>25,289,016.8</t>
+  </si>
+  <si>
+    <t>SPL</t>
+  </si>
+  <si>
+    <t>17,916,375.0</t>
   </si>
   <si>
     <t>MHCL</t>
   </si>
   <si>
-    <t>14,520,229.4</t>
+    <t>14,482,205.4</t>
   </si>
   <si>
     <t>NGPL</t>
   </si>
   <si>
-    <t>13,984,076.0</t>
-  </si>
-  <si>
-    <t>PHCL</t>
-  </si>
-  <si>
-    <t>8,080,210.8</t>
+    <t>13,950,976.0</t>
+  </si>
+  <si>
+    <t>SGIC</t>
+  </si>
+  <si>
+    <t>8,982,729.0</t>
+  </si>
+  <si>
+    <t>DORDI</t>
+  </si>
+  <si>
+    <t>82,641,609.0</t>
+  </si>
+  <si>
+    <t>MANDU</t>
+  </si>
+  <si>
+    <t>23,910,120.0</t>
+  </si>
+  <si>
+    <t>MKCL</t>
+  </si>
+  <si>
+    <t>14,362,064.0</t>
+  </si>
+  <si>
+    <t>9,916,161.3</t>
+  </si>
+  <si>
+    <t>HRL</t>
+  </si>
+  <si>
+    <t>4,845,430.09</t>
+  </si>
+  <si>
+    <t>SHPC</t>
+  </si>
+  <si>
+    <t>162,059,783.0</t>
+  </si>
+  <si>
+    <t>MEN</t>
+  </si>
+  <si>
+    <t>14,786,413.0</t>
+  </si>
+  <si>
+    <t>NRN</t>
+  </si>
+  <si>
+    <t>14,071,910.0</t>
+  </si>
+  <si>
+    <t>NRIC</t>
+  </si>
+  <si>
+    <t>11,489,357.2</t>
+  </si>
+  <si>
+    <t>NMB</t>
+  </si>
+  <si>
+    <t>6,885,280.0</t>
+  </si>
+  <si>
+    <t>GUFL</t>
+  </si>
+  <si>
+    <t>18,828,072.0</t>
+  </si>
+  <si>
+    <t>GBIME</t>
+  </si>
+  <si>
+    <t>17,602,348.0</t>
+  </si>
+  <si>
+    <t>17,367,437.5</t>
+  </si>
+  <si>
+    <t>NICA</t>
+  </si>
+  <si>
+    <t>3,605,757.5</t>
+  </si>
+  <si>
+    <t>HDL</t>
+  </si>
+  <si>
+    <t>3,415,649.4</t>
+  </si>
+  <si>
+    <t>NIL</t>
+  </si>
+  <si>
+    <t>23,580,254.8</t>
+  </si>
+  <si>
+    <t>JOSHI</t>
+  </si>
+  <si>
+    <t>17,014,988.8</t>
+  </si>
+  <si>
+    <t>11,354,000.0</t>
+  </si>
+  <si>
+    <t>NABIL</t>
+  </si>
+  <si>
+    <t>9,239,154.0</t>
+  </si>
+  <si>
+    <t>PMHPL</t>
+  </si>
+  <si>
+    <t>7,169,089.5</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>4,800,500.59</t>
+  </si>
+  <si>
+    <t>4,397,600.0</t>
+  </si>
+  <si>
+    <t>3,287,807.0</t>
+  </si>
+  <si>
+    <t>BHPL</t>
+  </si>
+  <si>
+    <t>2,497,345.0</t>
+  </si>
+  <si>
+    <t>RLFL</t>
+  </si>
+  <si>
+    <t>2,222,736.1</t>
+  </si>
+  <si>
+    <t>CGH</t>
+  </si>
+  <si>
+    <t>24,771,241.0</t>
+  </si>
+  <si>
+    <t>RIDI</t>
+  </si>
+  <si>
+    <t>22,627,298.1</t>
+  </si>
+  <si>
+    <t>IHL</t>
+  </si>
+  <si>
+    <t>8,621,262.0</t>
+  </si>
+  <si>
+    <t>5,724,659.0</t>
+  </si>
+  <si>
+    <t>IGI</t>
+  </si>
+  <si>
+    <t>5,401,359.5</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
   </si>
   <si>
     <t>SMJC</t>
   </si>
   <si>
-    <t>155,988,791.0</t>
-  </si>
-  <si>
-    <t>NFS</t>
-  </si>
-  <si>
-    <t>22,242,000.0</t>
-  </si>
-  <si>
-    <t>NIMB</t>
-  </si>
-  <si>
-    <t>7,733,973.0</t>
-  </si>
-  <si>
-    <t>SONA</t>
-  </si>
-  <si>
-    <t>7,138,326.0</t>
-  </si>
-  <si>
-    <t>IGI</t>
-  </si>
-  <si>
-    <t>6,235,109.5</t>
-  </si>
-  <si>
-    <t>MKHL</t>
-  </si>
-  <si>
-    <t>15,807,443.0</t>
-  </si>
-  <si>
-    <t>10,480,750.0</t>
+    <t>65,672,662.0</t>
+  </si>
+  <si>
+    <t>AKJCL</t>
+  </si>
+  <si>
+    <t>55,604,862.0</t>
+  </si>
+  <si>
+    <t>33,068,555.0</t>
+  </si>
+  <si>
+    <t>19,281,657.7</t>
+  </si>
+  <si>
+    <t>19,168,064.8</t>
+  </si>
+  <si>
+    <t>48,082,564.0</t>
+  </si>
+  <si>
+    <t>KDL</t>
+  </si>
+  <si>
+    <t>30,487,196.6</t>
+  </si>
+  <si>
+    <t>26,547,601.0</t>
+  </si>
+  <si>
+    <t>KBL</t>
+  </si>
+  <si>
+    <t>13,841,541.0</t>
+  </si>
+  <si>
+    <t>12,373,986.0</t>
+  </si>
+  <si>
+    <t>HHL</t>
+  </si>
+  <si>
+    <t>7,123,886.0</t>
+  </si>
+  <si>
+    <t>5,638,528.5</t>
+  </si>
+  <si>
+    <t>2,189,690.0</t>
+  </si>
+  <si>
+    <t>SNLI</t>
+  </si>
+  <si>
+    <t>1,694,310.2</t>
+  </si>
+  <si>
+    <t>GVL</t>
+  </si>
+  <si>
+    <t>1,689,994.0</t>
+  </si>
+  <si>
+    <t>62,469,373.0</t>
+  </si>
+  <si>
+    <t>21,671,660.0</t>
+  </si>
+  <si>
+    <t>19,009,017.6</t>
+  </si>
+  <si>
+    <t>HATHY</t>
+  </si>
+  <si>
+    <t>6,454,672.4</t>
+  </si>
+  <si>
+    <t>ULHC</t>
+  </si>
+  <si>
+    <t>4,750,778.0</t>
+  </si>
+  <si>
+    <t>16,205,970.0</t>
+  </si>
+  <si>
+    <t>12,061,855.7</t>
+  </si>
+  <si>
+    <t>9,207,430.69</t>
+  </si>
+  <si>
+    <t>8,911,114.1</t>
   </si>
   <si>
     <t>USHEC</t>
   </si>
   <si>
-    <t>9,647,089.5</t>
-  </si>
-  <si>
-    <t>HRL</t>
-  </si>
-  <si>
-    <t>7,420,450.3</t>
-  </si>
-  <si>
-    <t>SHL</t>
-  </si>
-  <si>
-    <t>7,362,253.6</t>
-  </si>
-  <si>
-    <t>HDHPC</t>
-  </si>
-  <si>
-    <t>23,058,771.5</t>
-  </si>
-  <si>
-    <t>13,880,990.0</t>
-  </si>
-  <si>
-    <t>HDL</t>
-  </si>
-  <si>
-    <t>12,450,079.4</t>
-  </si>
-  <si>
-    <t>9,913,791.5</t>
-  </si>
-  <si>
-    <t>DHPL</t>
-  </si>
-  <si>
-    <t>4,904,280.0</t>
-  </si>
-  <si>
-    <t>100,188,884.2</t>
-  </si>
-  <si>
-    <t>20,230,160.0</t>
-  </si>
-  <si>
-    <t>BHL</t>
-  </si>
-  <si>
-    <t>8,009,830.4</t>
-  </si>
-  <si>
-    <t>SICL</t>
-  </si>
-  <si>
-    <t>5,725,812.8</t>
-  </si>
-  <si>
-    <t>HURJA</t>
-  </si>
-  <si>
-    <t>1,878,779.0</t>
-  </si>
-  <si>
-    <t>15,595,100.0</t>
-  </si>
-  <si>
-    <t>SPC</t>
-  </si>
-  <si>
-    <t>7,798,100.0</t>
-  </si>
-  <si>
-    <t>BEDC</t>
-  </si>
-  <si>
-    <t>6,015,763.0</t>
-  </si>
-  <si>
-    <t>JOSHI</t>
-  </si>
-  <si>
-    <t>4,795,889.5</t>
-  </si>
-  <si>
-    <t>GBLBS</t>
-  </si>
-  <si>
-    <t>2,093,040.0</t>
-  </si>
-  <si>
-    <t>LSL</t>
-  </si>
-  <si>
-    <t>25,290,146.6</t>
-  </si>
-  <si>
-    <t>MNBBL</t>
-  </si>
-  <si>
-    <t>11,255,409.6</t>
-  </si>
-  <si>
-    <t>6,650,525.2</t>
-  </si>
-  <si>
-    <t>5,378,283.0</t>
-  </si>
-  <si>
-    <t>BARUN</t>
-  </si>
-  <si>
-    <t>4,256,037.0</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>34,478,103.6</t>
-  </si>
-  <si>
-    <t>22,192,989.4</t>
-  </si>
-  <si>
-    <t>17,769,108.2</t>
+    <t>4,438,798.5</t>
+  </si>
+  <si>
+    <t>169,079,283.6</t>
+  </si>
+  <si>
+    <t>3,420,412.0</t>
+  </si>
+  <si>
+    <t>TVCL</t>
+  </si>
+  <si>
+    <t>1,836,969.0</t>
   </si>
   <si>
     <t>CIT</t>
   </si>
   <si>
-    <t>15,932,085.0</t>
-  </si>
-  <si>
-    <t>SPIL</t>
-  </si>
-  <si>
-    <t>13,942,000.0</t>
-  </si>
-  <si>
-    <t>9,658,586.4</t>
-  </si>
-  <si>
-    <t>7,650,045.0</t>
-  </si>
-  <si>
-    <t>4,918,154.0</t>
-  </si>
-  <si>
-    <t>DORDI</t>
+    <t>1,063,384.2</t>
+  </si>
+  <si>
+    <t>ILI</t>
+  </si>
+  <si>
+    <t>1,009,261.0</t>
+  </si>
+  <si>
+    <t>10,590,831.8</t>
+  </si>
+  <si>
+    <t>7,813,589.4</t>
+  </si>
+  <si>
+    <t>5,006,187.59</t>
   </si>
   <si>
     <t>4,458,617.5</t>
   </si>
   <si>
-    <t>2,977,747.0</t>
-  </si>
-  <si>
-    <t>29,222,665.3</t>
-  </si>
-  <si>
-    <t>26,929,726.3</t>
-  </si>
-  <si>
-    <t>API</t>
-  </si>
-  <si>
-    <t>10,597,730.1</t>
-  </si>
-  <si>
-    <t>9,398,771.19</t>
-  </si>
-  <si>
-    <t>4,444,736.5</t>
-  </si>
-  <si>
-    <t>14,772,813.6</t>
-  </si>
-  <si>
-    <t>8,206,872.6</t>
-  </si>
-  <si>
-    <t>8,032,003.0</t>
-  </si>
-  <si>
-    <t>HATHY</t>
-  </si>
-  <si>
-    <t>6,472,802.4</t>
-  </si>
-  <si>
-    <t>ULHC</t>
-  </si>
-  <si>
-    <t>4,757,618.0</t>
-  </si>
-  <si>
-    <t>74,837,246.8</t>
-  </si>
-  <si>
-    <t>NICLBSL</t>
-  </si>
-  <si>
-    <t>2,745,281.0</t>
-  </si>
-  <si>
-    <t>TVCL</t>
-  </si>
-  <si>
-    <t>1,763,200.0</t>
-  </si>
-  <si>
-    <t>1,122,173.0</t>
-  </si>
-  <si>
-    <t>1,097,952.0</t>
-  </si>
-  <si>
-    <t>95,777,279.0</t>
-  </si>
-  <si>
-    <t>16,519,699.0</t>
-  </si>
-  <si>
-    <t>SPDL</t>
-  </si>
-  <si>
-    <t>10,214,823.8</t>
-  </si>
-  <si>
-    <t>7,451,245.5</t>
-  </si>
-  <si>
-    <t>4,793,440.0</t>
-  </si>
-  <si>
-    <t>JFL</t>
-  </si>
-  <si>
-    <t>12,409,190.0</t>
-  </si>
-  <si>
-    <t>7,868,715.4</t>
-  </si>
-  <si>
-    <t>7,304,476.6</t>
-  </si>
-  <si>
-    <t>KBLPO</t>
-  </si>
-  <si>
-    <t>5,828,092.0</t>
-  </si>
-  <si>
-    <t>5,174,769.0</t>
+    <t>4,433,068.5</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -521,97 +530,97 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>344,972,253.4</t>
-  </si>
-  <si>
-    <t>213,166,893.9</t>
-  </si>
-  <si>
-    <t>88,711,234.1</t>
-  </si>
-  <si>
-    <t>76,187,566.0</t>
-  </si>
-  <si>
-    <t>75,504,258.9</t>
+    <t>370,178,368.0</t>
+  </si>
+  <si>
+    <t>241,227,348.2</t>
+  </si>
+  <si>
+    <t>182,829,111.1</t>
+  </si>
+  <si>
+    <t>118,466,283.0</t>
+  </si>
+  <si>
+    <t>97,167,605.5</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>1,534,614,493.0</t>
+    <t>1,448,333,722.8</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>1,062,726,742.0</t>
+    <t>1,387,344,664.1</t>
+  </si>
+  <si>
+    <t>Commercial Banks</t>
+  </si>
+  <si>
+    <t>159,705,139.3</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>202,618,635.6</t>
-  </si>
-  <si>
-    <t>Commercial Banks</t>
-  </si>
-  <si>
-    <t>139,536,241.0</t>
+    <t>130,935,943.4</t>
+  </si>
+  <si>
+    <t>Investment</t>
+  </si>
+  <si>
+    <t>111,175,162.9</t>
+  </si>
+  <si>
+    <t>Non Life Insurance</t>
+  </si>
+  <si>
+    <t>99,983,207.3</t>
+  </si>
+  <si>
+    <t>Manufacturing And Processing</t>
+  </si>
+  <si>
+    <t>97,040,394.5</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>122,853,298.9</t>
-  </si>
-  <si>
-    <t>Investment</t>
-  </si>
-  <si>
-    <t>120,162,819.6</t>
-  </si>
-  <si>
-    <t>Manufacturing And Processing</t>
-  </si>
-  <si>
-    <t>110,607,997.2</t>
+    <t>79,248,017.2</t>
+  </si>
+  <si>
+    <t>Microfinance</t>
+  </si>
+  <si>
+    <t>71,457,834.0</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
   </si>
   <si>
-    <t>98,077,116.6</t>
-  </si>
-  <si>
-    <t>Microfinance</t>
-  </si>
-  <si>
-    <t>93,008,872.4</t>
-  </si>
-  <si>
-    <t>Non Life Insurance</t>
-  </si>
-  <si>
-    <t>84,161,240.8</t>
+    <t>56,156,523.2</t>
   </si>
   <si>
     <t>Life Insurance</t>
   </si>
   <si>
-    <t>66,146,640.0</t>
+    <t>47,706,642.0</t>
   </si>
   <si>
     <t>Others</t>
   </si>
   <si>
-    <t>38,394,933.4</t>
+    <t>41,751,121.7</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>4,876,118.26</t>
+    <t>4,676,485.26</t>
   </si>
   <si>
     <t>Trading</t>
@@ -635,214 +644,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>107,059,722.4</t>
-  </si>
-  <si>
-    <t>50,557,398.2</t>
-  </si>
-  <si>
-    <t>5,868,635.1</t>
-  </si>
-  <si>
-    <t>5,485,774.2</t>
-  </si>
-  <si>
-    <t>4,477,470.59</t>
-  </si>
-  <si>
-    <t>207,179,590.2</t>
-  </si>
-  <si>
-    <t>40,367,294.1</t>
-  </si>
-  <si>
-    <t>27,490,811.8</t>
-  </si>
-  <si>
-    <t>7,697,344.4</t>
-  </si>
-  <si>
-    <t>7,650,326.5</t>
-  </si>
-  <si>
-    <t>46,594,986.9</t>
-  </si>
-  <si>
-    <t>43,709,919.2</t>
-  </si>
-  <si>
-    <t>7,787,572.6</t>
-  </si>
-  <si>
-    <t>6,112,304.0</t>
-  </si>
-  <si>
-    <t>5,091,071.9</t>
-  </si>
-  <si>
-    <t>63,900,350.1</t>
-  </si>
-  <si>
-    <t>32,574,183.1</t>
-  </si>
-  <si>
-    <t>13,202,290.4</t>
-  </si>
-  <si>
-    <t>8,026,195.1</t>
-  </si>
-  <si>
-    <t>4,404,166.8</t>
-  </si>
-  <si>
-    <t>106,853,885.2</t>
-  </si>
-  <si>
-    <t>34,466,453.5</t>
-  </si>
-  <si>
-    <t>6,588,088.8</t>
-  </si>
-  <si>
-    <t>3,518,992.5</t>
-  </si>
-  <si>
-    <t>1,477,892.3</t>
-  </si>
-  <si>
-    <t>31,642,330.1</t>
-  </si>
-  <si>
-    <t>21,545,595.9</t>
-  </si>
-  <si>
-    <t>4,406,804.2</t>
-  </si>
-  <si>
-    <t>3,400,042.2</t>
-  </si>
-  <si>
-    <t>2,905,832.6</t>
-  </si>
-  <si>
-    <t>49,804,271.7</t>
-  </si>
-  <si>
-    <t>28,829,481.7</t>
-  </si>
-  <si>
-    <t>15,443,941.4</t>
-  </si>
-  <si>
-    <t>4,015,188.1</t>
-  </si>
-  <si>
-    <t>3,574,848.0</t>
-  </si>
-  <si>
-    <t>87,187,869.0</t>
-  </si>
-  <si>
-    <t>85,036,748.0</t>
-  </si>
-  <si>
-    <t>39,504,900.2</t>
-  </si>
-  <si>
-    <t>25,684,644.6</t>
-  </si>
-  <si>
-    <t>18,719,186.0</t>
-  </si>
-  <si>
-    <t>35,416,435.9</t>
-  </si>
-  <si>
-    <t>32,739,180.8</t>
-  </si>
-  <si>
-    <t>8,007,840.0</t>
-  </si>
-  <si>
-    <t>7,945,893.0</t>
+    <t>81,107,867.59</t>
+  </si>
+  <si>
+    <t>68,879,242.5</t>
+  </si>
+  <si>
+    <t>11,030,333.7</t>
+  </si>
+  <si>
+    <t>5,005,465.7</t>
+  </si>
+  <si>
+    <t>4,745,775.0</t>
+  </si>
+  <si>
+    <t>102,300,809.2</t>
+  </si>
+  <si>
+    <t>74,877,455.9</t>
+  </si>
+  <si>
+    <t>11,902,196.0</t>
+  </si>
+  <si>
+    <t>5,185,069.59</t>
+  </si>
+  <si>
+    <t>3,287,262.4</t>
+  </si>
+  <si>
+    <t>191,533,962.5</t>
+  </si>
+  <si>
+    <t>25,614,845.9</t>
+  </si>
+  <si>
+    <t>14,696,290.8</t>
+  </si>
+  <si>
+    <t>13,109,267.4</t>
+  </si>
+  <si>
+    <t>13,014,380.0</t>
+  </si>
+  <si>
+    <t>50,612,172.7</t>
+  </si>
+  <si>
+    <t>23,914,544.2</t>
+  </si>
+  <si>
+    <t>21,194,069.8</t>
+  </si>
+  <si>
+    <t>6,664,158.5</t>
+  </si>
+  <si>
+    <t>4,944,272.4</t>
+  </si>
+  <si>
+    <t>41,417,290.1</t>
+  </si>
+  <si>
+    <t>25,401,694.8</t>
+  </si>
+  <si>
+    <t>20,449,443.2</t>
+  </si>
+  <si>
+    <t>12,478,181.3</t>
+  </si>
+  <si>
+    <t>11,214,790.6</t>
+  </si>
+  <si>
+    <t>24,279,099.6</t>
+  </si>
+  <si>
+    <t>9,607,723.8</t>
+  </si>
+  <si>
+    <t>4,154,278.1</t>
+  </si>
+  <si>
+    <t>3,390,284.0</t>
+  </si>
+  <si>
+    <t>1,576,736.0</t>
+  </si>
+  <si>
+    <t>51,721,544.3</t>
+  </si>
+  <si>
+    <t>39,419,457.79</t>
+  </si>
+  <si>
+    <t>24,856,524.0</t>
+  </si>
+  <si>
+    <t>11,135,441.8</t>
+  </si>
+  <si>
+    <t>9,102,035.9</t>
+  </si>
+  <si>
+    <t>181,697,743.1</t>
+  </si>
+  <si>
+    <t>121,876,454.4</t>
+  </si>
+  <si>
+    <t>21,045,968.5</t>
+  </si>
+  <si>
+    <t>16,931,056.39</t>
+  </si>
+  <si>
+    <t>8,600,123.6</t>
+  </si>
+  <si>
+    <t>120,041,390.1</t>
+  </si>
+  <si>
+    <t>51,824,736.0</t>
+  </si>
+  <si>
+    <t>28,366,583.8</t>
+  </si>
+  <si>
+    <t>4,883,094.59</t>
+  </si>
+  <si>
+    <t>3,864,244.9</t>
+  </si>
+  <si>
+    <t>17,936,255.39</t>
+  </si>
+  <si>
+    <t>13,607,693.5</t>
+  </si>
+  <si>
+    <t>3,220,800.8</t>
+  </si>
+  <si>
+    <t>1,829,995.2</t>
+  </si>
+  <si>
+    <t>1,393,780.5</t>
+  </si>
+  <si>
+    <t>117,822,546.4</t>
+  </si>
+  <si>
+    <t>21,999,821.2</t>
+  </si>
+  <si>
+    <t>21,731,860.0</t>
+  </si>
+  <si>
+    <t>5,133,639.0</t>
+  </si>
+  <si>
+    <t>3,240,787.5</t>
+  </si>
+  <si>
+    <t>60,421,879.0</t>
+  </si>
+  <si>
+    <t>42,696,957.6</t>
+  </si>
+  <si>
+    <t>7,951,419.9</t>
+  </si>
+  <si>
+    <t>4,979,380.59</t>
+  </si>
+  <si>
+    <t>3,528,805.3</t>
+  </si>
+  <si>
+    <t>177,305,412.0</t>
+  </si>
+  <si>
+    <t>13,211,887.5</t>
+  </si>
+  <si>
+    <t>2,075,350.0</t>
+  </si>
+  <si>
+    <t>2,028,945.7</t>
+  </si>
+  <si>
+    <t>1,687,662.7</t>
+  </si>
+  <si>
+    <t>29,158,997.5</t>
+  </si>
+  <si>
+    <t>25,660,795.0</t>
+  </si>
+  <si>
+    <t>11,215,751.8</t>
+  </si>
+  <si>
+    <t>7,152,765.3</t>
   </si>
   <si>
     <t>3,932,865.0</t>
-  </si>
-  <si>
-    <t>104,982,933.0</t>
-  </si>
-  <si>
-    <t>29,241,054.7</t>
-  </si>
-  <si>
-    <t>5,185,024.0</t>
-  </si>
-  <si>
-    <t>5,057,454.2</t>
-  </si>
-  <si>
-    <t>4,849,480.4</t>
-  </si>
-  <si>
-    <t>51,284,552.1</t>
-  </si>
-  <si>
-    <t>49,515,480.8</t>
-  </si>
-  <si>
-    <t>5,896,429.5</t>
-  </si>
-  <si>
-    <t>3,991,037.5</t>
-  </si>
-  <si>
-    <t>2,697,257.8</t>
-  </si>
-  <si>
-    <t>82,461,743.0</t>
-  </si>
-  <si>
-    <t>5,708,780.9</t>
-  </si>
-  <si>
-    <t>3,140,615.0</t>
-  </si>
-  <si>
-    <t>1,442,188.0</t>
-  </si>
-  <si>
-    <t>1,292,550.89</t>
-  </si>
-  <si>
-    <t>113,953,324.7</t>
-  </si>
-  <si>
-    <t>43,137,776.0</t>
-  </si>
-  <si>
-    <t>7,343,312.7</t>
-  </si>
-  <si>
-    <t>4,846,070.2</t>
-  </si>
-  <si>
-    <t>3,120,419.5</t>
-  </si>
-  <si>
-    <t>39,813,208.2</t>
-  </si>
-  <si>
-    <t>34,114,607.0</t>
-  </si>
-  <si>
-    <t>16,622,191.1</t>
-  </si>
-  <si>
-    <t>8,152,297.5</t>
-  </si>
-  <si>
-    <t>4,380,139.0</t>
   </si>
 </sst>
 </file>
@@ -1429,27 +1438,27 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="4" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
       <c r="T4" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
@@ -1459,37 +1468,37 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
       <c r="T5" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U5" s="6"/>
       <c r="V5" s="6"/>
@@ -1499,37 +1508,37 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
       <c r="N6" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
       <c r="T6" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="U6" s="7"/>
       <c r="V6" s="7"/>
@@ -1539,164 +1548,164 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
       <c r="N7" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
       <c r="Q7" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R7" s="8"/>
       <c r="S7" s="8"/>
       <c r="T7" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="U7" s="8"/>
       <c r="V7" s="8"/>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="E8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="H8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="J8" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="J8" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="K8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="L8" s="5" t="s">
+      <c r="M8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="M8" s="5" t="s">
-        <v>53</v>
-      </c>
       <c r="N8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="O8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="O8" s="6" t="s">
+      <c r="P8" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="P8" s="6" t="s">
-        <v>53</v>
-      </c>
       <c r="Q8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="R8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="R8" s="5" t="s">
+      <c r="S8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="S8" s="5" t="s">
-        <v>53</v>
-      </c>
       <c r="T8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="U8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="U8" s="6" t="s">
+      <c r="V8" s="6" t="s">
         <v>52</v>
-      </c>
-      <c r="V8" s="6" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>55</v>
-      </c>
       <c r="D9" s="10">
-        <v>0.07030356379572142</v>
+        <v>0.04526358470084193</v>
       </c>
       <c r="E9" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>65</v>
-      </c>
       <c r="G9" s="12">
-        <v>0.3777660746183426</v>
+        <v>0.1903321511361234</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J9" s="14">
-        <v>0.05524553004052398</v>
+        <v>0.4833738259394568</v>
       </c>
       <c r="K9" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="L9" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="L9" s="15" t="s">
-        <v>84</v>
-      </c>
       <c r="M9" s="16">
-        <v>0.08833364602945598</v>
+        <v>0.0620975880784968</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P9" s="18">
-        <v>0.3891833102419086</v>
+        <v>0.09168842002446845</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="S9" s="16">
-        <v>0.06138851453616302</v>
+        <v>0.01918319207546554</v>
       </c>
       <c r="T9" s="17" t="s">
         <v>108</v>
@@ -1705,64 +1714,64 @@
         <v>109</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1125376482863707</v>
+        <v>0.1004492108385866</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>57</v>
-      </c>
       <c r="D10" s="10">
-        <v>0.06027528088111958</v>
+        <v>0.03206765070220313</v>
       </c>
       <c r="E10" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>67</v>
-      </c>
       <c r="G10" s="12">
-        <v>0.05386459487118645</v>
+        <v>0.0550674730149899</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J10" s="14">
-        <v>0.0366292378199448</v>
+        <v>0.04410326171873821</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="L10" s="15" t="s">
         <v>85</v>
       </c>
       <c r="M10" s="16">
-        <v>0.05317535919892429</v>
+        <v>0.05805498063308617</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="P10" s="18">
-        <v>0.07858397364528638</v>
+        <v>0.06616033003197347</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="S10" s="16">
-        <v>0.03069642228677295</v>
+        <v>0.01757316840478413</v>
       </c>
       <c r="T10" s="17" t="s">
         <v>110</v>
@@ -1771,121 +1780,121 @@
         <v>111</v>
       </c>
       <c r="V10" s="18">
-        <v>0.05008501322344412</v>
+        <v>0.09175536411576839</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>59</v>
-      </c>
       <c r="D11" s="10">
-        <v>0.03015197174533935</v>
+        <v>0.02592099708589266</v>
       </c>
       <c r="E11" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>69</v>
-      </c>
       <c r="G11" s="12">
-        <v>0.01872976002111746</v>
+        <v>0.03307731503478686</v>
       </c>
       <c r="H11" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="I11" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="I11" s="13" t="s">
-        <v>78</v>
-      </c>
       <c r="J11" s="14">
-        <v>0.03371567259650238</v>
+        <v>0.04197212194820538</v>
       </c>
       <c r="K11" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="L11" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="L11" s="15" t="s">
-        <v>87</v>
-      </c>
       <c r="M11" s="16">
-        <v>0.04769382040835184</v>
+        <v>0.05728021328227544</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P11" s="18">
-        <v>0.03111415337579207</v>
+        <v>0.04414839151601597</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="R11" s="15" t="s">
         <v>103</v>
       </c>
       <c r="S11" s="16">
-        <v>0.02368043516050629</v>
+        <v>0.01313834502761236</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="V11" s="18">
-        <v>0.02959391567454358</v>
+        <v>0.03495985382132025</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>61</v>
-      </c>
       <c r="D12" s="10">
-        <v>0.0290386227945323</v>
+        <v>0.02497017534645368</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G12" s="12">
-        <v>0.01728725105873829</v>
+        <v>0.02283794246118536</v>
       </c>
       <c r="H12" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="I12" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="I12" s="13" t="s">
-        <v>80</v>
-      </c>
       <c r="J12" s="14">
-        <v>0.02593377752258004</v>
+        <v>0.03426917181142371</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="L12" s="15" t="s">
         <v>88</v>
       </c>
       <c r="M12" s="16">
-        <v>0.03797779726343312</v>
+        <v>0.01189228742836497</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P12" s="18">
-        <v>0.02224189636528052</v>
+        <v>0.03592511784998811</v>
       </c>
       <c r="Q12" s="15" t="s">
         <v>104</v>
@@ -1894,46 +1903,46 @@
         <v>105</v>
       </c>
       <c r="S12" s="16">
-        <v>0.01887852801742737</v>
+        <v>0.00997959438099091</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="V12" s="18">
-        <v>0.02393261416043221</v>
+        <v>0.02321391483252746</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>63</v>
-      </c>
       <c r="D13" s="10">
-        <v>0.01677895582958117</v>
+        <v>0.01607775099173524</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G13" s="12">
-        <v>0.0150998852259233</v>
+        <v>0.011159525392502</v>
       </c>
       <c r="H13" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="I13" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="I13" s="13" t="s">
-        <v>82</v>
-      </c>
       <c r="J13" s="14">
-        <v>0.02573038551679458</v>
+        <v>0.02053664440772714</v>
       </c>
       <c r="K13" s="15" t="s">
         <v>89</v>
@@ -1942,16 +1951,16 @@
         <v>90</v>
       </c>
       <c r="M13" s="16">
-        <v>0.0187873379789266</v>
+        <v>0.01126528459535128</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P13" s="18">
-        <v>0.007298109328908792</v>
+        <v>0.02787597058828247</v>
       </c>
       <c r="Q13" s="15" t="s">
         <v>106</v>
@@ -1960,624 +1969,624 @@
         <v>107</v>
       </c>
       <c r="S13" s="16">
-        <v>0.008239037676242579</v>
+        <v>0.008882234810963504</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="V13" s="18">
-        <v>0.01893877495355366</v>
+        <v>0.0219029114944424</v>
       </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="C15" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S15" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T15" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="V15" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D16" s="10">
-        <v>0.07159548082484722</v>
+        <v>0.1175443127139195</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G16" s="12">
-        <v>0.02339069523713476</v>
+        <v>0.1107391052642783</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="J16" s="14">
-        <v>0.102130473201474</v>
+        <v>0.02124833174296261</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="M16" s="16">
-        <v>0.05659176107458862</v>
+        <v>0.2060326406270366</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="P16" s="18">
-        <v>0.290704978616926</v>
+        <v>0.06301457710558475</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="S16" s="16">
-        <v>0.377017453182451</v>
+        <v>0.6756546126212152</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>156</v>
+        <v>89</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="V16" s="18">
-        <v>0.05521917614106469</v>
+        <v>0.04294660475162338</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D17" s="10">
-        <v>0.0460848359140535</v>
+        <v>0.09952444576317521</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G17" s="12">
-        <v>0.01852650726874137</v>
+        <v>0.07021515893994644</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J17" s="14">
-        <v>0.09411686654759652</v>
+        <v>0.01681797323962643</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="M17" s="16">
-        <v>0.03143892463036208</v>
+        <v>0.07147613497851697</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>144</v>
+        <v>70</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="P17" s="18">
-        <v>0.01066403279820355</v>
+        <v>0.04690078631788698</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="S17" s="16">
-        <v>0.06502810383995856</v>
+        <v>0.01366824542699302</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="V17" s="18">
-        <v>0.03501469327784556</v>
+        <v>0.0316846818068883</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D18" s="10">
-        <v>0.03689842864233795</v>
+        <v>0.05918780283213501</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G18" s="12">
-        <v>0.01191054638630092</v>
+        <v>0.06114186385012785</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>132</v>
+        <v>76</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J18" s="14">
-        <v>0.03703807229296447</v>
+        <v>0.006531162842056682</v>
       </c>
       <c r="K18" s="15" t="s">
         <v>70</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M18" s="16">
-        <v>0.03076903337671431</v>
+        <v>0.06269437171802274</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P18" s="18">
-        <v>0.00684914317688881</v>
+        <v>0.03580176637310066</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="S18" s="16">
-        <v>0.04020960810322755</v>
+        <v>0.007340678004222281</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="V18" s="18">
-        <v>0.03250390879611685</v>
+        <v>0.02030046026882213</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D19" s="10">
-        <v>0.03308375945936121</v>
+        <v>0.03451130399330475</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G19" s="12">
-        <v>0.01079766321927354</v>
+        <v>0.03187849686673996</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J19" s="14">
-        <v>0.03284782343821272</v>
+        <v>0.005053599286272315</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="M19" s="16">
-        <v>0.02479604067459592</v>
+        <v>0.02128840318205934</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P19" s="18">
-        <v>0.004359076421414954</v>
+        <v>0.03464958200904441</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>79</v>
+        <v>157</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="S19" s="16">
-        <v>0.02933106505820862</v>
+        <v>0.004249370025829236</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="V19" s="18">
-        <v>0.02593420188701519</v>
+        <v>0.01808002309234778</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D20" s="10">
-        <v>0.02895124990749259</v>
+        <v>0.03430798957063553</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G20" s="12">
-        <v>0.007211362997207573</v>
+        <v>0.02849856630342562</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="J20" s="14">
-        <v>0.01553393700884852</v>
+        <v>0.005040725406837835</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="M20" s="16">
-        <v>0.01822550452678575</v>
+        <v>0.01566872355790783</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>86</v>
+        <v>151</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="P20" s="18">
-        <v>0.004264990046138511</v>
+        <v>0.0172596277997802</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>104</v>
+        <v>159</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="S20" s="16">
-        <v>0.01886888581145522</v>
+        <v>0.004033089302660733</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="V20" s="18">
-        <v>0.02302700505837377</v>
+        <v>0.01797642001135094</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D31" s="22">
-        <v>0.4064749353216175</v>
+        <v>0.3836216580676118</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D32" s="22">
-        <v>0.2814855363932779</v>
+        <v>0.3674674227182857</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D33" s="22">
-        <v>0.0536678085448424</v>
+        <v>0.04230126619004727</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D34" s="22">
-        <v>0.03695910914057596</v>
+        <v>0.03468113937901535</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D35" s="22">
-        <v>0.03254028093192578</v>
+        <v>0.02944708091529004</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D36" s="22">
-        <v>0.03182765088415804</v>
+        <v>0.02648265600637422</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D37" s="22">
-        <v>0.0292968551470103</v>
+        <v>0.02570319012227115</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D38" s="22">
-        <v>0.02597778778211744</v>
+        <v>0.02099050465942422</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D39" s="22">
-        <v>0.02463535667463984</v>
+        <v>0.01892711074075128</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D40" s="22">
-        <v>0.02229187529950369</v>
+        <v>0.01487423665013368</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D41" s="22">
-        <v>0.0175203292673076</v>
+        <v>0.01263610783673315</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D42" s="22">
-        <v>0.01016970590440189</v>
+        <v>0.01105866298671303</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D43" s="22">
-        <v>0.001291542512767607</v>
+        <v>0.001238665512626399</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D44" s="22">
         <v>0.0009904826018646467</v>
@@ -2585,10 +2594,10 @@
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D45" s="22">
         <v>0.0001068383823163383</v>
@@ -2596,13 +2605,13 @@
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -2765,27 +2774,27 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="4" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
       <c r="T4" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
@@ -2795,37 +2804,37 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
       <c r="T5" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U5" s="6"/>
       <c r="V5" s="6"/>
@@ -2835,37 +2844,37 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
       <c r="N6" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
       <c r="T6" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="U6" s="7"/>
       <c r="V6" s="7"/>
@@ -2875,835 +2884,835 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
       <c r="N7" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
       <c r="Q7" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R7" s="8"/>
       <c r="S7" s="8"/>
       <c r="T7" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="U7" s="8"/>
       <c r="V7" s="8"/>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="E8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="H8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="J8" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="J8" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="K8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="L8" s="5" t="s">
+      <c r="M8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="M8" s="5" t="s">
-        <v>53</v>
-      </c>
       <c r="N8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="O8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="O8" s="6" t="s">
+      <c r="P8" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="P8" s="6" t="s">
-        <v>53</v>
-      </c>
       <c r="Q8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="R8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="R8" s="5" t="s">
+      <c r="S8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="S8" s="5" t="s">
-        <v>53</v>
-      </c>
       <c r="T8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="U8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="U8" s="6" t="s">
+      <c r="V8" s="6" t="s">
         <v>52</v>
-      </c>
-      <c r="V8" s="6" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D9" s="10">
-        <v>0.2223147882821103</v>
+        <v>0.1451710386390851</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="G9" s="12">
-        <v>0.5017374647829076</v>
+        <v>0.2356093173113573</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="J9" s="14">
-        <v>0.1628451071132612</v>
+        <v>0.5712861176111129</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="M9" s="16">
-        <v>0.2447897498308491</v>
+        <v>0.1669259524863906</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="P9" s="18">
-        <v>0.4150734793226181</v>
+        <v>0.1610451593154141</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1245567929222588</v>
+        <v>0.09702126295873365</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="V9" s="18">
-        <v>0.2216221084196264</v>
+        <v>0.2097346801594639</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D10" s="10">
-        <v>0.1049849282714687</v>
+        <v>0.1232836156377808</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G10" s="12">
-        <v>0.09775955142264793</v>
+        <v>0.1724505055685353</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="J10" s="14">
-        <v>0.1527620662135221</v>
+        <v>0.07640110232365674</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M10" s="16">
-        <v>0.1247853277723008</v>
+        <v>0.07887347758265449</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P10" s="18">
-        <v>0.1338847974257489</v>
+        <v>0.09877082677477074</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="S10" s="16">
-        <v>0.08481203243951269</v>
+        <v>0.03839324820903505</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="V10" s="18">
-        <v>0.1282871990877649</v>
+        <v>0.1598488112765512</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D11" s="10">
-        <v>0.01218650992655162</v>
+        <v>0.01974265933931054</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G11" s="12">
-        <v>0.06657591225101304</v>
+        <v>0.02741198526185234</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="J11" s="14">
-        <v>0.02721683551324914</v>
+        <v>0.04383445528317683</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="M11" s="16">
-        <v>0.05057539370524076</v>
+        <v>0.06990097637970097</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="P11" s="18">
-        <v>0.02559140395488747</v>
+        <v>0.07951471064630354</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="S11" s="16">
-        <v>0.01734693356821849</v>
+        <v>0.01660083423949578</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="V11" s="18">
-        <v>0.06872339939020043</v>
+        <v>0.1007950396990764</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D12" s="10">
-        <v>0.01139148040455281</v>
+        <v>0.008959040300811894</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G12" s="12">
-        <v>0.01864105465740472</v>
+        <v>0.01194175019944879</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="J12" s="14">
-        <v>0.02136192895010375</v>
+        <v>0.03910085908483165</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="M12" s="16">
-        <v>0.0307467844471573</v>
+        <v>0.02197931734182943</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="P12" s="18">
-        <v>0.01366951195037313</v>
+        <v>0.04851960837063846</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="S12" s="16">
-        <v>0.01338391802670504</v>
+        <v>0.01354785148081798</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="V12" s="18">
-        <v>0.01786703071944316</v>
+        <v>0.04515503850408668</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D13" s="10">
-        <v>0.009297688301108217</v>
+        <v>0.008494232511389612</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G13" s="12">
-        <v>0.01852718899176341</v>
+        <v>0.007570904433151776</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="J13" s="14">
-        <v>0.01779281858488546</v>
+        <v>0.03881783954276891</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M13" s="16">
-        <v>0.01687150207312137</v>
+        <v>0.01630689487713244</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="P13" s="18">
-        <v>0.005740866585028081</v>
+        <v>0.04360709584101952</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01143851253308773</v>
+        <v>0.006300765703539593</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="V13" s="18">
-        <v>0.01590757828589399</v>
+        <v>0.03690942747597847</v>
       </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="C15" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S15" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T15" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="V15" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D16" s="10">
-        <v>0.1810499056319557</v>
+        <v>0.3252119783778493</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G16" s="12">
-        <v>0.08576980359386942</v>
+        <v>0.2764677053069423</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="J16" s="14">
-        <v>0.3669055000732134</v>
+        <v>0.05349825993365202</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="M16" s="16">
-        <v>0.1964610938609888</v>
+        <v>0.3885950697823323</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P16" s="18">
-        <v>0.3203223028713751</v>
+        <v>0.2349417623943406</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="S16" s="16">
-        <v>0.4485655962315122</v>
+        <v>0.7085268928860363</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="V16" s="18">
-        <v>0.1771632601593401</v>
+        <v>0.1182418873450595</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D17" s="10">
-        <v>0.1765829968920148</v>
+        <v>0.2181407549530632</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="G17" s="12">
-        <v>0.07928615727931508</v>
+        <v>0.1193577134363598</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="J17" s="14">
-        <v>0.1021947424289592</v>
+        <v>0.04058750880412124</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="M17" s="16">
-        <v>0.1896841275332263</v>
+        <v>0.07255845604787262</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P17" s="18">
-        <v>0.02217573601950327</v>
+        <v>0.1660209618343785</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="S17" s="16">
-        <v>0.1698074388130723</v>
+        <v>0.05279578042172148</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="V17" s="18">
-        <v>0.1518052743906894</v>
+        <v>0.1040564179744063</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D18" s="10">
-        <v>0.08203387162966246</v>
+        <v>0.03766915832848833</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="G18" s="12">
-        <v>0.01939299781464265</v>
+        <v>0.06533116889141292</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="J18" s="14">
-        <v>0.01812117235866913</v>
+        <v>0.009606645007570219</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="M18" s="16">
-        <v>0.02258806876552995</v>
+        <v>0.07167468291281026</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="P18" s="18">
-        <v>0.0121997061016814</v>
+        <v>0.03091794952029598</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="S18" s="16">
-        <v>0.02890619864108217</v>
+        <v>0.00829326792997743</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="V18" s="18">
-        <v>0.07396644730247001</v>
+        <v>0.04548070148247548</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D19" s="10">
-        <v>0.0533354299669868</v>
+        <v>0.0303040767261514</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G19" s="12">
-        <v>0.01924297758001962</v>
+        <v>0.01124627062160888</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="J19" s="14">
-        <v>0.01767532787780251</v>
+        <v>0.005458305354357049</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="M19" s="16">
-        <v>0.01528888448438309</v>
+        <v>0.01693145214049034</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="P19" s="18">
-        <v>0.005602173377944034</v>
+        <v>0.01936160333239867</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="S19" s="16">
-        <v>0.01907605920551753</v>
+        <v>0.008107832561002053</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="V19" s="18">
-        <v>0.03627659433104508</v>
+        <v>0.02900499130013818</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D20" s="10">
-        <v>0.03887131200335938</v>
+        <v>0.0153929441419134</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="G20" s="12">
-        <v>0.009524421360851933</v>
+        <v>0.008899754654266158</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="J20" s="14">
-        <v>0.01694847896140649</v>
+        <v>0.004157212852770567</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="M20" s="16">
-        <v>0.01033266736501505</v>
+        <v>0.01068856584067351</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="P20" s="18">
-        <v>0.005020908675996195</v>
+        <v>0.01372125048160932</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S20" s="16">
-        <v>0.01228321189570292</v>
+        <v>0.006744037847365081</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="V20" s="18">
-        <v>0.0194910116585649</v>
+        <v>0.01594805789442273</v>
       </c>
     </row>
   </sheetData>
